--- a/credit structure.xlsx
+++ b/credit structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Law Preparation\NMIMS\Books\Sem 4\Attendance\attendance-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7C3A660-DA7C-41ED-BE42-C9D8FDCE50DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061FD31C-C223-4E33-BACB-740985878A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0DD9671E-DA0B-4AE1-AC63-1CE00A2B95EE}"/>
   </bookViews>
@@ -173,7 +173,7 @@
     <t>COMPANY LAW I</t>
   </si>
   <si>
-    <t>FAMILY LAW I (MARRIAGE AND DIVORCE LAWS)</t>
+    <t xml:space="preserve">FAMILY LAW I </t>
   </si>
 </sst>
 </file>

--- a/credit structure.xlsx
+++ b/credit structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Law Preparation\NMIMS\Books\Sem 4\Attendance\attendance-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061FD31C-C223-4E33-BACB-740985878A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AE1D5D-A476-413C-8116-25A810F44BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0DD9671E-DA0B-4AE1-AC63-1CE00A2B95EE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="65">
   <si>
     <t>Program</t>
   </si>
@@ -174,6 +174,63 @@
   </si>
   <si>
     <t xml:space="preserve">FAMILY LAW I </t>
+  </si>
+  <si>
+    <t>B.B.A., LL.B.(Hons.)</t>
+  </si>
+  <si>
+    <t>PRINCIPLES OF MANAGEMENT</t>
+  </si>
+  <si>
+    <t>PRINCIPLES OF MARKETING</t>
+  </si>
+  <si>
+    <t>FINANCIAL ACCOUNTING</t>
+  </si>
+  <si>
+    <t>BUSINESS ENVIRONMENT</t>
+  </si>
+  <si>
+    <t>STRATEGIC MANAGEMENT</t>
+  </si>
+  <si>
+    <t>CUSTOMER RELATIONSHIP MANAGEMENT</t>
+  </si>
+  <si>
+    <t>COST ACCOUNTING</t>
+  </si>
+  <si>
+    <t>ICT &amp; BUSINESS MANAGEMENT</t>
+  </si>
+  <si>
+    <t>HINDI</t>
+  </si>
+  <si>
+    <t>MARATHI</t>
+  </si>
+  <si>
+    <t>BUSINESS ETHICS &amp; CSR</t>
+  </si>
+  <si>
+    <t>ENVIRONMENTAL MANAGEMENT</t>
+  </si>
+  <si>
+    <t>CONSUMER BEHAVIOUR</t>
+  </si>
+  <si>
+    <t>MANAGEMENT ACCOUNTING</t>
+  </si>
+  <si>
+    <t>HUMAN RESOURCE MANAGEMENT</t>
+  </si>
+  <si>
+    <t>ENTREPRENEURIAL MANAGEMENT</t>
+  </si>
+  <si>
+    <t>INTEGRATED MARKETING MANAGEMENT</t>
+  </si>
+  <si>
+    <t>FINANCIAL MANAGEMENT</t>
   </si>
 </sst>
 </file>
@@ -217,9 +274,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -557,821 +613,1694 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E2EE3E5-444D-4613-80D9-3783316A4EAB}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="34.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.21875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.44140625" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" customWidth="1"/>
+    <col min="3" max="3" width="34.6640625" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" customWidth="1"/>
+    <col min="6" max="6" width="12.21875" customWidth="1"/>
+    <col min="7" max="7" width="19.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1">
-        <v>45</v>
-      </c>
-      <c r="F2" s="1">
-        <v>15</v>
-      </c>
-      <c r="G2" s="1">
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>45</v>
+      </c>
+      <c r="F2">
+        <v>15</v>
+      </c>
+      <c r="G2">
         <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1">
-        <v>45</v>
-      </c>
-      <c r="F3" s="1">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1">
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>45</v>
+      </c>
+      <c r="F3">
+        <v>15</v>
+      </c>
+      <c r="G3">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="1">
-        <v>3</v>
-      </c>
-      <c r="E4" s="1">
-        <v>45</v>
-      </c>
-      <c r="F4" s="1">
-        <v>15</v>
-      </c>
-      <c r="G4" s="1">
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>45</v>
+      </c>
+      <c r="F4">
+        <v>15</v>
+      </c>
+      <c r="G4">
         <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="1">
-        <v>3</v>
-      </c>
-      <c r="E5" s="1">
-        <v>45</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1">
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>45</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6">
         <v>4</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6">
         <v>60</v>
       </c>
-      <c r="F6" s="1">
-        <v>15</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="F6">
+        <v>15</v>
+      </c>
+      <c r="G6">
         <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7">
         <v>4</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7">
         <v>60</v>
       </c>
-      <c r="F7" s="1">
-        <v>15</v>
-      </c>
-      <c r="G7" s="1">
+      <c r="F7">
+        <v>15</v>
+      </c>
+      <c r="G7">
         <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="1">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1">
-        <v>45</v>
-      </c>
-      <c r="F8" s="1">
-        <v>15</v>
-      </c>
-      <c r="G8" s="1">
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>45</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
         <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9">
         <v>2</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9">
         <v>30</v>
       </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="1">
-        <v>3</v>
-      </c>
-      <c r="E10" s="1">
-        <v>45</v>
-      </c>
-      <c r="F10" s="1">
-        <v>15</v>
-      </c>
-      <c r="G10" s="1">
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>45</v>
+      </c>
+      <c r="F10">
+        <v>15</v>
+      </c>
+      <c r="G10">
         <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="1">
-        <v>3</v>
-      </c>
-      <c r="E11" s="1">
-        <v>45</v>
-      </c>
-      <c r="F11" s="1">
-        <v>15</v>
-      </c>
-      <c r="G11" s="1">
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>45</v>
+      </c>
+      <c r="F11">
+        <v>15</v>
+      </c>
+      <c r="G11">
         <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="1">
-        <v>3</v>
-      </c>
-      <c r="E12" s="1">
-        <v>45</v>
-      </c>
-      <c r="F12" s="1">
-        <v>15</v>
-      </c>
-      <c r="G12" s="1">
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12">
+        <v>45</v>
+      </c>
+      <c r="F12">
+        <v>15</v>
+      </c>
+      <c r="G12">
         <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="1">
-        <v>3</v>
-      </c>
-      <c r="E13" s="1">
-        <v>45</v>
-      </c>
-      <c r="F13" s="1">
-        <v>15</v>
-      </c>
-      <c r="G13" s="1">
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13">
+        <v>45</v>
+      </c>
+      <c r="F13">
+        <v>15</v>
+      </c>
+      <c r="G13">
         <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14">
         <v>4</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14">
         <v>60</v>
       </c>
-      <c r="F14" s="1">
-        <v>15</v>
-      </c>
-      <c r="G14" s="1">
+      <c r="F14">
+        <v>15</v>
+      </c>
+      <c r="G14">
         <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="1">
-        <v>3</v>
-      </c>
-      <c r="E15" s="1">
-        <v>45</v>
-      </c>
-      <c r="F15" s="1">
-        <v>15</v>
-      </c>
-      <c r="G15" s="1">
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15">
+        <v>45</v>
+      </c>
+      <c r="F15">
+        <v>15</v>
+      </c>
+      <c r="G15">
         <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="1">
-        <v>3</v>
-      </c>
-      <c r="E16" s="1">
-        <v>45</v>
-      </c>
-      <c r="F16" s="1">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1">
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16">
+        <v>45</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
         <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="1" t="s">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17">
         <v>2</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17">
         <v>30</v>
       </c>
-      <c r="F17" s="1">
-        <v>0</v>
-      </c>
-      <c r="G17" s="1">
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
         <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="1" t="s">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="1">
-        <v>0</v>
-      </c>
-      <c r="E18" s="1">
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
         <v>30</v>
       </c>
-      <c r="F18" s="1">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1">
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>30</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>30</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C21" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="1">
-        <v>3</v>
-      </c>
-      <c r="E19" s="1">
-        <v>45</v>
-      </c>
-      <c r="F19" s="1">
-        <v>15</v>
-      </c>
-      <c r="G19" s="1">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <v>45</v>
+      </c>
+      <c r="F21">
+        <v>15</v>
+      </c>
+      <c r="G21">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C22" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D22">
         <v>2</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E22">
         <v>30</v>
       </c>
-      <c r="F20" s="1">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1">
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="1" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C23" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="1">
-        <v>3</v>
-      </c>
-      <c r="E21" s="1">
-        <v>45</v>
-      </c>
-      <c r="F21" s="1">
-        <v>15</v>
-      </c>
-      <c r="G21" s="1">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <v>45</v>
+      </c>
+      <c r="F23">
+        <v>15</v>
+      </c>
+      <c r="G23">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C24" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="1">
-        <v>3</v>
-      </c>
-      <c r="E22" s="1">
-        <v>45</v>
-      </c>
-      <c r="F22" s="1">
-        <v>15</v>
-      </c>
-      <c r="G22" s="1">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="1" t="s">
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24">
+        <v>45</v>
+      </c>
+      <c r="F24">
+        <v>15</v>
+      </c>
+      <c r="G24">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C25" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="1">
-        <v>3</v>
-      </c>
-      <c r="E23" s="1">
-        <v>45</v>
-      </c>
-      <c r="F23" s="1">
-        <v>15</v>
-      </c>
-      <c r="G23" s="1">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="1" t="s">
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25">
+        <v>45</v>
+      </c>
+      <c r="F25">
+        <v>15</v>
+      </c>
+      <c r="G25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C26" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="1">
-        <v>3</v>
-      </c>
-      <c r="E24" s="1">
-        <v>45</v>
-      </c>
-      <c r="F24" s="1">
-        <v>15</v>
-      </c>
-      <c r="G24" s="1">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="1" t="s">
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <v>45</v>
+      </c>
+      <c r="F26">
+        <v>15</v>
+      </c>
+      <c r="G26">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C27" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D27">
         <v>4</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E27">
         <v>60</v>
       </c>
-      <c r="F25" s="1">
-        <v>15</v>
-      </c>
-      <c r="G25" s="1">
+      <c r="F27">
+        <v>15</v>
+      </c>
+      <c r="G27">
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" s="1" t="s">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C28" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D28">
         <v>4</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E28">
         <v>60</v>
       </c>
-      <c r="F26" s="1">
-        <v>15</v>
-      </c>
-      <c r="G26" s="1">
+      <c r="F28">
+        <v>15</v>
+      </c>
+      <c r="G28">
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="1" t="s">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C29" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="1">
-        <v>3</v>
-      </c>
-      <c r="E27" s="1">
-        <v>45</v>
-      </c>
-      <c r="F27" s="1">
-        <v>15</v>
-      </c>
-      <c r="G27" s="1">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B28" s="1" t="s">
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29">
+        <v>45</v>
+      </c>
+      <c r="F29">
+        <v>15</v>
+      </c>
+      <c r="G29">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C30" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D30">
         <v>2</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E30">
         <v>30</v>
       </c>
-      <c r="F28" s="1">
-        <v>0</v>
-      </c>
-      <c r="G28" s="1">
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="1" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C31" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="1">
-        <v>3</v>
-      </c>
-      <c r="E29" s="1">
-        <v>45</v>
-      </c>
-      <c r="F29" s="1">
-        <v>15</v>
-      </c>
-      <c r="G29" s="1">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="1" t="s">
+      <c r="D31">
+        <v>3</v>
+      </c>
+      <c r="E31">
+        <v>45</v>
+      </c>
+      <c r="F31">
+        <v>15</v>
+      </c>
+      <c r="G31">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C32" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="1">
-        <v>3</v>
-      </c>
-      <c r="E30" s="1">
-        <v>45</v>
-      </c>
-      <c r="F30" s="1">
-        <v>15</v>
-      </c>
-      <c r="G30" s="1">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31" s="1" t="s">
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="E32">
+        <v>45</v>
+      </c>
+      <c r="F32">
+        <v>15</v>
+      </c>
+      <c r="G32">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C33" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="1">
-        <v>3</v>
-      </c>
-      <c r="E31" s="1">
-        <v>45</v>
-      </c>
-      <c r="F31" s="1">
-        <v>15</v>
-      </c>
-      <c r="G31" s="1">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" s="1" t="s">
+      <c r="D33">
+        <v>3</v>
+      </c>
+      <c r="E33">
+        <v>45</v>
+      </c>
+      <c r="F33">
+        <v>15</v>
+      </c>
+      <c r="G33">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D32" s="1">
-        <v>3</v>
-      </c>
-      <c r="E32" s="1">
-        <v>45</v>
-      </c>
-      <c r="F32" s="1">
-        <v>15</v>
-      </c>
-      <c r="G32" s="1">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" s="1" t="s">
+      <c r="C34" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34">
+        <v>45</v>
+      </c>
+      <c r="F34">
+        <v>15</v>
+      </c>
+      <c r="G34">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C35" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D35">
         <v>4</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E35">
         <v>60</v>
       </c>
-      <c r="F33" s="1">
-        <v>15</v>
-      </c>
-      <c r="G33" s="1">
+      <c r="F35">
+        <v>15</v>
+      </c>
+      <c r="G35">
         <v>53</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" s="1" t="s">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C36" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="1">
-        <v>3</v>
-      </c>
-      <c r="E34" s="1">
-        <v>45</v>
-      </c>
-      <c r="F34" s="1">
-        <v>15</v>
-      </c>
-      <c r="G34" s="1">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" s="1" t="s">
+      <c r="D36">
+        <v>3</v>
+      </c>
+      <c r="E36">
+        <v>45</v>
+      </c>
+      <c r="F36">
+        <v>15</v>
+      </c>
+      <c r="G36">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D35" s="1">
+      <c r="C37" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37">
         <v>4</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E37">
         <v>60</v>
       </c>
-      <c r="F35" s="1">
-        <v>15</v>
-      </c>
-      <c r="G35" s="1">
+      <c r="F37">
+        <v>15</v>
+      </c>
+      <c r="G37">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38">
+        <v>3</v>
+      </c>
+      <c r="E38">
+        <v>45</v>
+      </c>
+      <c r="F38">
+        <v>15</v>
+      </c>
+      <c r="G38">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39">
+        <v>3</v>
+      </c>
+      <c r="E39">
+        <v>45</v>
+      </c>
+      <c r="F39">
+        <v>15</v>
+      </c>
+      <c r="G39">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" t="s">
+        <v>49</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="E40">
+        <v>45</v>
+      </c>
+      <c r="F40">
+        <v>15</v>
+      </c>
+      <c r="G40">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="E41">
+        <v>45</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42">
+        <v>60</v>
+      </c>
+      <c r="F42">
+        <v>15</v>
+      </c>
+      <c r="G42">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43">
+        <v>4</v>
+      </c>
+      <c r="E43">
+        <v>60</v>
+      </c>
+      <c r="F43">
+        <v>15</v>
+      </c>
+      <c r="G43">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44">
+        <v>3</v>
+      </c>
+      <c r="E44">
+        <v>45</v>
+      </c>
+      <c r="F44">
+        <v>15</v>
+      </c>
+      <c r="G44">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>50</v>
+      </c>
+      <c r="D45">
+        <v>2</v>
+      </c>
+      <c r="E45">
+        <v>30</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" t="s">
+        <v>51</v>
+      </c>
+      <c r="D46">
+        <v>3</v>
+      </c>
+      <c r="E46">
+        <v>45</v>
+      </c>
+      <c r="F46">
+        <v>15</v>
+      </c>
+      <c r="G46">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <v>45</v>
+      </c>
+      <c r="F47">
+        <v>15</v>
+      </c>
+      <c r="G47">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" t="s">
+        <v>53</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48">
+        <v>45</v>
+      </c>
+      <c r="F48">
+        <v>15</v>
+      </c>
+      <c r="G48">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>46</v>
+      </c>
+      <c r="B49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49">
+        <v>45</v>
+      </c>
+      <c r="F49">
+        <v>15</v>
+      </c>
+      <c r="G49">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>46</v>
+      </c>
+      <c r="B50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50">
+        <v>4</v>
+      </c>
+      <c r="E50">
+        <v>60</v>
+      </c>
+      <c r="F50">
+        <v>15</v>
+      </c>
+      <c r="G50">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>46</v>
+      </c>
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51">
+        <v>3</v>
+      </c>
+      <c r="E51">
+        <v>45</v>
+      </c>
+      <c r="F51">
+        <v>15</v>
+      </c>
+      <c r="G51">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>46</v>
+      </c>
+      <c r="B52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" t="s">
+        <v>23</v>
+      </c>
+      <c r="D52">
+        <v>3</v>
+      </c>
+      <c r="E52">
+        <v>45</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>46</v>
+      </c>
+      <c r="B53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" t="s">
+        <v>54</v>
+      </c>
+      <c r="D53">
+        <v>2</v>
+      </c>
+      <c r="E53">
+        <v>30</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>46</v>
+      </c>
+      <c r="B54" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" t="s">
+        <v>25</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>30</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>46</v>
+      </c>
+      <c r="B55" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" t="s">
+        <v>55</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>30</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>46</v>
+      </c>
+      <c r="B56" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" t="s">
+        <v>56</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>30</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>46</v>
+      </c>
+      <c r="B57" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57" t="s">
+        <v>57</v>
+      </c>
+      <c r="D57">
+        <v>3</v>
+      </c>
+      <c r="E57">
+        <v>45</v>
+      </c>
+      <c r="F57">
+        <v>15</v>
+      </c>
+      <c r="G57">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>46</v>
+      </c>
+      <c r="B58" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58" t="s">
+        <v>58</v>
+      </c>
+      <c r="D58">
+        <v>2</v>
+      </c>
+      <c r="E58">
+        <v>30</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>46</v>
+      </c>
+      <c r="B59" t="s">
+        <v>27</v>
+      </c>
+      <c r="C59" t="s">
+        <v>59</v>
+      </c>
+      <c r="D59">
+        <v>3</v>
+      </c>
+      <c r="E59">
+        <v>45</v>
+      </c>
+      <c r="F59">
+        <v>15</v>
+      </c>
+      <c r="G59">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>46</v>
+      </c>
+      <c r="B60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60" t="s">
+        <v>60</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60">
+        <v>45</v>
+      </c>
+      <c r="F60">
+        <v>15</v>
+      </c>
+      <c r="G60">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>46</v>
+      </c>
+      <c r="B61" t="s">
+        <v>27</v>
+      </c>
+      <c r="C61" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61">
+        <v>3</v>
+      </c>
+      <c r="E61">
+        <v>45</v>
+      </c>
+      <c r="F61">
+        <v>15</v>
+      </c>
+      <c r="G61">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>46</v>
+      </c>
+      <c r="B62" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62" t="s">
+        <v>33</v>
+      </c>
+      <c r="D62">
+        <v>3</v>
+      </c>
+      <c r="E62">
+        <v>45</v>
+      </c>
+      <c r="F62">
+        <v>15</v>
+      </c>
+      <c r="G62">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>46</v>
+      </c>
+      <c r="B63" t="s">
+        <v>27</v>
+      </c>
+      <c r="C63" t="s">
+        <v>34</v>
+      </c>
+      <c r="D63">
+        <v>4</v>
+      </c>
+      <c r="E63">
+        <v>60</v>
+      </c>
+      <c r="F63">
+        <v>15</v>
+      </c>
+      <c r="G63">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>46</v>
+      </c>
+      <c r="B64" t="s">
+        <v>27</v>
+      </c>
+      <c r="C64" t="s">
+        <v>35</v>
+      </c>
+      <c r="D64">
+        <v>4</v>
+      </c>
+      <c r="E64">
+        <v>60</v>
+      </c>
+      <c r="F64">
+        <v>15</v>
+      </c>
+      <c r="G64">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>46</v>
+      </c>
+      <c r="B65" t="s">
+        <v>36</v>
+      </c>
+      <c r="C65" t="s">
+        <v>61</v>
+      </c>
+      <c r="D65">
+        <v>3</v>
+      </c>
+      <c r="E65">
+        <v>45</v>
+      </c>
+      <c r="F65">
+        <v>15</v>
+      </c>
+      <c r="G65">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>46</v>
+      </c>
+      <c r="B66" t="s">
+        <v>36</v>
+      </c>
+      <c r="C66" t="s">
+        <v>62</v>
+      </c>
+      <c r="D66">
+        <v>2</v>
+      </c>
+      <c r="E66">
+        <v>30</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>46</v>
+      </c>
+      <c r="B67" t="s">
+        <v>36</v>
+      </c>
+      <c r="C67" t="s">
+        <v>63</v>
+      </c>
+      <c r="D67">
+        <v>3</v>
+      </c>
+      <c r="E67">
+        <v>45</v>
+      </c>
+      <c r="F67">
+        <v>15</v>
+      </c>
+      <c r="G67">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>46</v>
+      </c>
+      <c r="B68" t="s">
+        <v>36</v>
+      </c>
+      <c r="C68" t="s">
+        <v>64</v>
+      </c>
+      <c r="D68">
+        <v>3</v>
+      </c>
+      <c r="E68">
+        <v>45</v>
+      </c>
+      <c r="F68">
+        <v>15</v>
+      </c>
+      <c r="G68">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>46</v>
+      </c>
+      <c r="B69" t="s">
+        <v>36</v>
+      </c>
+      <c r="C69" t="s">
+        <v>41</v>
+      </c>
+      <c r="D69">
+        <v>3</v>
+      </c>
+      <c r="E69">
+        <v>45</v>
+      </c>
+      <c r="F69">
+        <v>15</v>
+      </c>
+      <c r="G69">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>46</v>
+      </c>
+      <c r="B70" t="s">
+        <v>36</v>
+      </c>
+      <c r="C70" t="s">
+        <v>42</v>
+      </c>
+      <c r="D70">
+        <v>3</v>
+      </c>
+      <c r="E70">
+        <v>45</v>
+      </c>
+      <c r="F70">
+        <v>15</v>
+      </c>
+      <c r="G70">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>46</v>
+      </c>
+      <c r="B71" t="s">
+        <v>36</v>
+      </c>
+      <c r="C71" t="s">
+        <v>43</v>
+      </c>
+      <c r="D71">
+        <v>4</v>
+      </c>
+      <c r="E71">
+        <v>60</v>
+      </c>
+      <c r="F71">
+        <v>15</v>
+      </c>
+      <c r="G71">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>46</v>
+      </c>
+      <c r="B72" t="s">
+        <v>36</v>
+      </c>
+      <c r="C72" t="s">
+        <v>44</v>
+      </c>
+      <c r="D72">
+        <v>3</v>
+      </c>
+      <c r="E72">
+        <v>45</v>
+      </c>
+      <c r="F72">
+        <v>15</v>
+      </c>
+      <c r="G72">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>46</v>
+      </c>
+      <c r="B73" t="s">
+        <v>36</v>
+      </c>
+      <c r="C73" t="s">
+        <v>45</v>
+      </c>
+      <c r="D73">
+        <v>4</v>
+      </c>
+      <c r="E73">
+        <v>60</v>
+      </c>
+      <c r="F73">
+        <v>15</v>
+      </c>
+      <c r="G73">
         <v>53</v>
       </c>
     </row>

--- a/credit structure.xlsx
+++ b/credit structure.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Law Preparation\NMIMS\Books\Sem 4\Attendance\attendance-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AE1D5D-A476-413C-8116-25A810F44BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A51AE9-2849-471E-9EE9-799623A7A817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0DD9671E-DA0B-4AE1-AC63-1CE00A2B95EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$113</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="89">
   <si>
     <t>Program</t>
   </si>
@@ -56,9 +59,6 @@
     <t>Total Tutorials (U1)</t>
   </si>
   <si>
-    <t>Required Cumulative Attendance</t>
-  </si>
-  <si>
     <t>B.A., LL.B.(Hons.)</t>
   </si>
   <si>
@@ -231,6 +231,81 @@
   </si>
   <si>
     <t>FINANCIAL MANAGEMENT</t>
+  </si>
+  <si>
+    <t>Semester V</t>
+  </si>
+  <si>
+    <t>FAMILY LAW II</t>
+  </si>
+  <si>
+    <t>CPC &amp; LIMITATION ACT</t>
+  </si>
+  <si>
+    <t>BANKING &amp; INSURANCE LAW</t>
+  </si>
+  <si>
+    <t>THE BHARATIYA SAKSHYA ADHINIYAM, 2023</t>
+  </si>
+  <si>
+    <t>ENIVRONMENTAL LAW</t>
+  </si>
+  <si>
+    <t>COMPANY LAW II</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIVE LAW</t>
+  </si>
+  <si>
+    <t>CYBER LAW</t>
+  </si>
+  <si>
+    <t>MARITIME LAW</t>
+  </si>
+  <si>
+    <t>MEDIA &amp; ENTERTAINMENT LAW</t>
+  </si>
+  <si>
+    <t>SPORTS LAW</t>
+  </si>
+  <si>
+    <t>Semester VI</t>
+  </si>
+  <si>
+    <t>INTELLECTUAL PROPERTY LAW</t>
+  </si>
+  <si>
+    <t>HUMAN RIGHTS</t>
+  </si>
+  <si>
+    <t>PUBLIC INTERNATIONAL LAW</t>
+  </si>
+  <si>
+    <t>ALTERNATE DISPUTE RESOLUTION (CLINICAL)</t>
+  </si>
+  <si>
+    <t>INTERNATIONAL HUMANITARIAN LAW AND REFUGE LAW</t>
+  </si>
+  <si>
+    <t>INTERNATIONAL TRADE LAW</t>
+  </si>
+  <si>
+    <t>AIR &amp; SPACE LAW</t>
+  </si>
+  <si>
+    <t>LAW AND TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>PRIVATE INTERNATIONAL LAW</t>
+  </si>
+  <si>
+    <t>Required Cumulative Attendance (70%)</t>
+  </si>
+  <si>
+    <t>Required Cumulative Attendance (75%)</t>
+  </si>
+  <si>
+    <t>Required Cumulative Attendance (80%)</t>
   </si>
 </sst>
 </file>
@@ -613,7 +688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E2EE3E5-444D-4613-80D9-3783316A4EAB}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
@@ -623,9 +698,11 @@
     <col min="5" max="5" width="12.77734375" customWidth="1"/>
     <col min="6" max="6" width="12.21875" customWidth="1"/>
     <col min="7" max="7" width="19.44140625" customWidth="1"/>
+    <col min="8" max="8" width="18.21875" customWidth="1"/>
+    <col min="9" max="9" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -645,87 +722,111 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>45</v>
+      </c>
+      <c r="F2">
+        <v>15</v>
+      </c>
+      <c r="G2">
+        <v>42</v>
+      </c>
+      <c r="H2">
+        <v>45</v>
+      </c>
+      <c r="I2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>45</v>
-      </c>
-      <c r="F2">
-        <v>15</v>
-      </c>
-      <c r="G2">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>45</v>
+      </c>
+      <c r="F3">
+        <v>15</v>
+      </c>
+      <c r="G3">
+        <v>42</v>
+      </c>
+      <c r="H3">
+        <v>45</v>
+      </c>
+      <c r="I3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>45</v>
-      </c>
-      <c r="F3">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>45</v>
+      </c>
+      <c r="F4">
+        <v>15</v>
+      </c>
+      <c r="G4">
+        <v>42</v>
+      </c>
+      <c r="H4">
+        <v>45</v>
+      </c>
+      <c r="I4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>11</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>45</v>
-      </c>
-      <c r="F4">
-        <v>15</v>
-      </c>
-      <c r="G4">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -739,16 +840,22 @@
       <c r="G5">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5">
+        <v>45</v>
+      </c>
+      <c r="I5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -762,16 +869,22 @@
       <c r="G6">
         <v>53</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6">
+        <v>57</v>
+      </c>
+      <c r="I6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7">
         <v>4</v>
@@ -785,16 +898,22 @@
       <c r="G7">
         <v>53</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7">
+        <v>57</v>
+      </c>
+      <c r="I7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -808,16 +927,22 @@
       <c r="G8">
         <v>42</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H8">
+        <v>45</v>
+      </c>
+      <c r="I8">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
         <v>7</v>
       </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -831,108 +956,138 @@
       <c r="G9">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9">
+        <v>23</v>
+      </c>
+      <c r="I9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>45</v>
+      </c>
+      <c r="F10">
+        <v>15</v>
+      </c>
+      <c r="G10">
+        <v>42</v>
+      </c>
+      <c r="H10">
+        <v>45</v>
+      </c>
+      <c r="I10">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
         <v>17</v>
       </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10">
-        <v>45</v>
-      </c>
-      <c r="F10">
-        <v>15</v>
-      </c>
-      <c r="G10">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>45</v>
+      </c>
+      <c r="F11">
+        <v>15</v>
+      </c>
+      <c r="G11">
+        <v>42</v>
+      </c>
+      <c r="H11">
+        <v>45</v>
+      </c>
+      <c r="I11">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
         <v>18</v>
       </c>
-      <c r="D11">
-        <v>3</v>
-      </c>
-      <c r="E11">
-        <v>45</v>
-      </c>
-      <c r="F11">
-        <v>15</v>
-      </c>
-      <c r="G11">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12">
+        <v>45</v>
+      </c>
+      <c r="F12">
+        <v>15</v>
+      </c>
+      <c r="G12">
+        <v>42</v>
+      </c>
+      <c r="H12">
+        <v>45</v>
+      </c>
+      <c r="I12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
         <v>19</v>
       </c>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12">
-        <v>45</v>
-      </c>
-      <c r="F12">
-        <v>15</v>
-      </c>
-      <c r="G12">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13">
+        <v>45</v>
+      </c>
+      <c r="F13">
+        <v>15</v>
+      </c>
+      <c r="G13">
+        <v>42</v>
+      </c>
+      <c r="H13">
+        <v>45</v>
+      </c>
+      <c r="I13">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
         <v>20</v>
-      </c>
-      <c r="D13">
-        <v>3</v>
-      </c>
-      <c r="E13">
-        <v>45</v>
-      </c>
-      <c r="F13">
-        <v>15</v>
-      </c>
-      <c r="G13">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" t="s">
-        <v>21</v>
       </c>
       <c r="D14">
         <v>4</v>
@@ -946,39 +1101,51 @@
       <c r="G14">
         <v>53</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14">
+        <v>57</v>
+      </c>
+      <c r="I14">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15">
+        <v>45</v>
+      </c>
+      <c r="F15">
+        <v>15</v>
+      </c>
+      <c r="G15">
+        <v>42</v>
+      </c>
+      <c r="H15">
+        <v>45</v>
+      </c>
+      <c r="I15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
         <v>22</v>
-      </c>
-      <c r="D15">
-        <v>3</v>
-      </c>
-      <c r="E15">
-        <v>45</v>
-      </c>
-      <c r="F15">
-        <v>15</v>
-      </c>
-      <c r="G15">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
-        <v>23</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -992,16 +1159,22 @@
       <c r="G16">
         <v>32</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16">
+        <v>45</v>
+      </c>
+      <c r="I16">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -1015,16 +1188,22 @@
       <c r="G17">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17">
+        <v>23</v>
+      </c>
+      <c r="I17">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1038,16 +1217,22 @@
       <c r="G18">
         <v>21</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18">
+        <v>23</v>
+      </c>
+      <c r="I18">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1061,16 +1246,22 @@
       <c r="G19">
         <v>21</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H19">
+        <v>23</v>
+      </c>
+      <c r="I19">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1084,39 +1275,51 @@
       <c r="G20">
         <v>21</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H20">
+        <v>23</v>
+      </c>
+      <c r="I20">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" t="s">
         <v>27</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <v>45</v>
+      </c>
+      <c r="F21">
+        <v>15</v>
+      </c>
+      <c r="G21">
+        <v>42</v>
+      </c>
+      <c r="H21">
+        <v>45</v>
+      </c>
+      <c r="I21">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
         <v>28</v>
-      </c>
-      <c r="D21">
-        <v>3</v>
-      </c>
-      <c r="E21">
-        <v>45</v>
-      </c>
-      <c r="F21">
-        <v>15</v>
-      </c>
-      <c r="G21">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" t="s">
-        <v>29</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -1130,108 +1333,138 @@
       <c r="G22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22">
+        <v>23</v>
+      </c>
+      <c r="I22">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <v>45</v>
+      </c>
+      <c r="F23">
+        <v>15</v>
+      </c>
+      <c r="G23">
+        <v>42</v>
+      </c>
+      <c r="H23">
+        <v>45</v>
+      </c>
+      <c r="I23">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" t="s">
         <v>30</v>
       </c>
-      <c r="D23">
-        <v>3</v>
-      </c>
-      <c r="E23">
-        <v>45</v>
-      </c>
-      <c r="F23">
-        <v>15</v>
-      </c>
-      <c r="G23">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24">
+        <v>45</v>
+      </c>
+      <c r="F24">
+        <v>15</v>
+      </c>
+      <c r="G24">
+        <v>42</v>
+      </c>
+      <c r="H24">
+        <v>45</v>
+      </c>
+      <c r="I24">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" t="s">
         <v>31</v>
       </c>
-      <c r="D24">
-        <v>3</v>
-      </c>
-      <c r="E24">
-        <v>45</v>
-      </c>
-      <c r="F24">
-        <v>15</v>
-      </c>
-      <c r="G24">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25">
+        <v>45</v>
+      </c>
+      <c r="F25">
+        <v>15</v>
+      </c>
+      <c r="G25">
+        <v>42</v>
+      </c>
+      <c r="H25">
+        <v>45</v>
+      </c>
+      <c r="I25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" t="s">
         <v>32</v>
       </c>
-      <c r="D25">
-        <v>3</v>
-      </c>
-      <c r="E25">
-        <v>45</v>
-      </c>
-      <c r="F25">
-        <v>15</v>
-      </c>
-      <c r="G25">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <v>45</v>
+      </c>
+      <c r="F26">
+        <v>15</v>
+      </c>
+      <c r="G26">
+        <v>42</v>
+      </c>
+      <c r="H26">
+        <v>45</v>
+      </c>
+      <c r="I26">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
         <v>33</v>
-      </c>
-      <c r="D26">
-        <v>3</v>
-      </c>
-      <c r="E26">
-        <v>45</v>
-      </c>
-      <c r="F26">
-        <v>15</v>
-      </c>
-      <c r="G26">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" t="s">
-        <v>34</v>
       </c>
       <c r="D27">
         <v>4</v>
@@ -1245,16 +1478,22 @@
       <c r="G27">
         <v>53</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H27">
+        <v>57</v>
+      </c>
+      <c r="I27">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D28">
         <v>4</v>
@@ -1268,39 +1507,51 @@
       <c r="G28">
         <v>53</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H28">
+        <v>57</v>
+      </c>
+      <c r="I28">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" t="s">
         <v>36</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29">
+        <v>45</v>
+      </c>
+      <c r="F29">
+        <v>15</v>
+      </c>
+      <c r="G29">
+        <v>42</v>
+      </c>
+      <c r="H29">
+        <v>45</v>
+      </c>
+      <c r="I29">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" t="s">
         <v>37</v>
-      </c>
-      <c r="D29">
-        <v>3</v>
-      </c>
-      <c r="E29">
-        <v>45</v>
-      </c>
-      <c r="F29">
-        <v>15</v>
-      </c>
-      <c r="G29">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" t="s">
-        <v>38</v>
       </c>
       <c r="D30">
         <v>2</v>
@@ -1314,86 +1565,110 @@
       <c r="G30">
         <v>21</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H30">
+        <v>23</v>
+      </c>
+      <c r="I30">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31">
+        <v>3</v>
+      </c>
+      <c r="E31">
+        <v>45</v>
+      </c>
+      <c r="F31">
+        <v>15</v>
+      </c>
+      <c r="G31">
+        <v>42</v>
+      </c>
+      <c r="H31">
+        <v>45</v>
+      </c>
+      <c r="I31">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" t="s">
         <v>39</v>
       </c>
-      <c r="D31">
-        <v>3</v>
-      </c>
-      <c r="E31">
-        <v>45</v>
-      </c>
-      <c r="F31">
-        <v>15</v>
-      </c>
-      <c r="G31">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="E32">
+        <v>45</v>
+      </c>
+      <c r="F32">
+        <v>15</v>
+      </c>
+      <c r="G32">
+        <v>42</v>
+      </c>
+      <c r="H32">
+        <v>45</v>
+      </c>
+      <c r="I32">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" t="s">
         <v>40</v>
       </c>
-      <c r="D32">
-        <v>3</v>
-      </c>
-      <c r="E32">
-        <v>45</v>
-      </c>
-      <c r="F32">
-        <v>15</v>
-      </c>
-      <c r="G32">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="D33">
+        <v>3</v>
+      </c>
+      <c r="E33">
+        <v>45</v>
+      </c>
+      <c r="F33">
+        <v>15</v>
+      </c>
+      <c r="G33">
+        <v>42</v>
+      </c>
+      <c r="H33">
+        <v>45</v>
+      </c>
+      <c r="I33">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" t="s">
         <v>41</v>
       </c>
-      <c r="D33">
-        <v>3</v>
-      </c>
-      <c r="E33">
-        <v>45</v>
-      </c>
-      <c r="F33">
-        <v>15</v>
-      </c>
-      <c r="G33">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" t="s">
-        <v>42</v>
-      </c>
       <c r="D34">
         <v>3</v>
       </c>
@@ -1406,16 +1681,22 @@
       <c r="G34">
         <v>42</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H34">
+        <v>45</v>
+      </c>
+      <c r="I34">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D35">
         <v>4</v>
@@ -1429,39 +1710,51 @@
       <c r="G35">
         <v>53</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H35">
+        <v>57</v>
+      </c>
+      <c r="I35">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36">
+        <v>3</v>
+      </c>
+      <c r="E36">
+        <v>45</v>
+      </c>
+      <c r="F36">
+        <v>15</v>
+      </c>
+      <c r="G36">
+        <v>42</v>
+      </c>
+      <c r="H36">
+        <v>45</v>
+      </c>
+      <c r="I36">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" t="s">
         <v>44</v>
-      </c>
-      <c r="D36">
-        <v>3</v>
-      </c>
-      <c r="E36">
-        <v>45</v>
-      </c>
-      <c r="F36">
-        <v>15</v>
-      </c>
-      <c r="G36">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" t="s">
-        <v>36</v>
-      </c>
-      <c r="C37" t="s">
-        <v>45</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -1475,40 +1768,52 @@
       <c r="G37">
         <v>53</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H37">
+        <v>57</v>
+      </c>
+      <c r="I37">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
         <v>46</v>
       </c>
-      <c r="B38" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="D38">
+        <v>3</v>
+      </c>
+      <c r="E38">
+        <v>45</v>
+      </c>
+      <c r="F38">
+        <v>15</v>
+      </c>
+      <c r="G38">
+        <v>42</v>
+      </c>
+      <c r="H38">
+        <v>45</v>
+      </c>
+      <c r="I38">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
         <v>47</v>
       </c>
-      <c r="D38">
-        <v>3</v>
-      </c>
-      <c r="E38">
-        <v>45</v>
-      </c>
-      <c r="F38">
-        <v>15</v>
-      </c>
-      <c r="G38">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" t="s">
-        <v>48</v>
-      </c>
       <c r="D39">
         <v>3</v>
       </c>
@@ -1521,16 +1826,22 @@
       <c r="G39">
         <v>42</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H39">
+        <v>45</v>
+      </c>
+      <c r="I39">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D40">
         <v>3</v>
@@ -1544,16 +1855,22 @@
       <c r="G40">
         <v>42</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H40">
+        <v>45</v>
+      </c>
+      <c r="I40">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D41">
         <v>3</v>
@@ -1567,16 +1884,22 @@
       <c r="G41">
         <v>32</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H41">
+        <v>45</v>
+      </c>
+      <c r="I41">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -1590,16 +1913,22 @@
       <c r="G42">
         <v>53</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H42">
+        <v>57</v>
+      </c>
+      <c r="I42">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -1613,16 +1942,22 @@
       <c r="G43">
         <v>53</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H43">
+        <v>57</v>
+      </c>
+      <c r="I43">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D44">
         <v>3</v>
@@ -1636,16 +1971,22 @@
       <c r="G44">
         <v>42</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H44">
+        <v>45</v>
+      </c>
+      <c r="I44">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -1659,63 +2000,81 @@
       <c r="G45">
         <v>21</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H45">
+        <v>23</v>
+      </c>
+      <c r="I45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C46" t="s">
+        <v>50</v>
+      </c>
+      <c r="D46">
+        <v>3</v>
+      </c>
+      <c r="E46">
+        <v>45</v>
+      </c>
+      <c r="F46">
+        <v>15</v>
+      </c>
+      <c r="G46">
+        <v>42</v>
+      </c>
+      <c r="H46">
+        <v>45</v>
+      </c>
+      <c r="I46">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" t="s">
         <v>51</v>
       </c>
-      <c r="D46">
-        <v>3</v>
-      </c>
-      <c r="E46">
-        <v>45</v>
-      </c>
-      <c r="F46">
-        <v>15</v>
-      </c>
-      <c r="G46">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>46</v>
-      </c>
-      <c r="B47" t="s">
-        <v>26</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <v>45</v>
+      </c>
+      <c r="F47">
+        <v>15</v>
+      </c>
+      <c r="G47">
+        <v>42</v>
+      </c>
+      <c r="H47">
+        <v>45</v>
+      </c>
+      <c r="I47">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>45</v>
+      </c>
+      <c r="B48" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" t="s">
         <v>52</v>
       </c>
-      <c r="D47">
-        <v>3</v>
-      </c>
-      <c r="E47">
-        <v>45</v>
-      </c>
-      <c r="F47">
-        <v>15</v>
-      </c>
-      <c r="G47">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>46</v>
-      </c>
-      <c r="B48" t="s">
-        <v>26</v>
-      </c>
-      <c r="C48" t="s">
-        <v>53</v>
-      </c>
       <c r="D48">
         <v>3</v>
       </c>
@@ -1728,39 +2087,51 @@
       <c r="G48">
         <v>42</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H48">
+        <v>45</v>
+      </c>
+      <c r="I48">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49">
+        <v>45</v>
+      </c>
+      <c r="F49">
+        <v>15</v>
+      </c>
+      <c r="G49">
+        <v>42</v>
+      </c>
+      <c r="H49">
+        <v>45</v>
+      </c>
+      <c r="I49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" t="s">
         <v>20</v>
-      </c>
-      <c r="D49">
-        <v>3</v>
-      </c>
-      <c r="E49">
-        <v>45</v>
-      </c>
-      <c r="F49">
-        <v>15</v>
-      </c>
-      <c r="G49">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>46</v>
-      </c>
-      <c r="B50" t="s">
-        <v>26</v>
-      </c>
-      <c r="C50" t="s">
-        <v>21</v>
       </c>
       <c r="D50">
         <v>4</v>
@@ -1774,39 +2145,51 @@
       <c r="G50">
         <v>53</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H50">
+        <v>57</v>
+      </c>
+      <c r="I50">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51">
+        <v>3</v>
+      </c>
+      <c r="E51">
+        <v>45</v>
+      </c>
+      <c r="F51">
+        <v>15</v>
+      </c>
+      <c r="G51">
+        <v>42</v>
+      </c>
+      <c r="H51">
+        <v>45</v>
+      </c>
+      <c r="I51">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" t="s">
         <v>22</v>
-      </c>
-      <c r="D51">
-        <v>3</v>
-      </c>
-      <c r="E51">
-        <v>45</v>
-      </c>
-      <c r="F51">
-        <v>15</v>
-      </c>
-      <c r="G51">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52" t="s">
-        <v>26</v>
-      </c>
-      <c r="C52" t="s">
-        <v>23</v>
       </c>
       <c r="D52">
         <v>3</v>
@@ -1820,16 +2203,22 @@
       <c r="G52">
         <v>32</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H52">
+        <v>45</v>
+      </c>
+      <c r="I52">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C53" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D53">
         <v>2</v>
@@ -1843,16 +2232,22 @@
       <c r="G53">
         <v>21</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H53">
+        <v>23</v>
+      </c>
+      <c r="I53">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -1866,16 +2261,22 @@
       <c r="G54">
         <v>21</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H54">
+        <v>23</v>
+      </c>
+      <c r="I54">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C55" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -1889,16 +2290,22 @@
       <c r="G55">
         <v>21</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H55">
+        <v>23</v>
+      </c>
+      <c r="I55">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C56" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -1912,39 +2319,51 @@
       <c r="G56">
         <v>21</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H56">
+        <v>23</v>
+      </c>
+      <c r="I56">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C57" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57">
+        <v>3</v>
+      </c>
+      <c r="E57">
+        <v>45</v>
+      </c>
+      <c r="F57">
+        <v>15</v>
+      </c>
+      <c r="G57">
+        <v>42</v>
+      </c>
+      <c r="H57">
+        <v>45</v>
+      </c>
+      <c r="I57">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>45</v>
+      </c>
+      <c r="B58" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" t="s">
         <v>57</v>
-      </c>
-      <c r="D57">
-        <v>3</v>
-      </c>
-      <c r="E57">
-        <v>45</v>
-      </c>
-      <c r="F57">
-        <v>15</v>
-      </c>
-      <c r="G57">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>46</v>
-      </c>
-      <c r="B58" t="s">
-        <v>27</v>
-      </c>
-      <c r="C58" t="s">
-        <v>58</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -1958,40 +2377,52 @@
       <c r="G58">
         <v>21</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H58">
+        <v>23</v>
+      </c>
+      <c r="I58">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C59" t="s">
+        <v>58</v>
+      </c>
+      <c r="D59">
+        <v>3</v>
+      </c>
+      <c r="E59">
+        <v>45</v>
+      </c>
+      <c r="F59">
+        <v>15</v>
+      </c>
+      <c r="G59">
+        <v>42</v>
+      </c>
+      <c r="H59">
+        <v>45</v>
+      </c>
+      <c r="I59">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60" t="s">
         <v>59</v>
       </c>
-      <c r="D59">
-        <v>3</v>
-      </c>
-      <c r="E59">
-        <v>45</v>
-      </c>
-      <c r="F59">
-        <v>15</v>
-      </c>
-      <c r="G59">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>46</v>
-      </c>
-      <c r="B60" t="s">
-        <v>27</v>
-      </c>
-      <c r="C60" t="s">
-        <v>60</v>
-      </c>
       <c r="D60">
         <v>3</v>
       </c>
@@ -2004,62 +2435,80 @@
       <c r="G60">
         <v>42</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H60">
+        <v>45</v>
+      </c>
+      <c r="I60">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C61" t="s">
+        <v>31</v>
+      </c>
+      <c r="D61">
+        <v>3</v>
+      </c>
+      <c r="E61">
+        <v>45</v>
+      </c>
+      <c r="F61">
+        <v>15</v>
+      </c>
+      <c r="G61">
+        <v>42</v>
+      </c>
+      <c r="H61">
+        <v>45</v>
+      </c>
+      <c r="I61">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" t="s">
         <v>32</v>
       </c>
-      <c r="D61">
-        <v>3</v>
-      </c>
-      <c r="E61">
-        <v>45</v>
-      </c>
-      <c r="F61">
-        <v>15</v>
-      </c>
-      <c r="G61">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>46</v>
-      </c>
-      <c r="B62" t="s">
-        <v>27</v>
-      </c>
-      <c r="C62" t="s">
+      <c r="D62">
+        <v>3</v>
+      </c>
+      <c r="E62">
+        <v>45</v>
+      </c>
+      <c r="F62">
+        <v>15</v>
+      </c>
+      <c r="G62">
+        <v>42</v>
+      </c>
+      <c r="H62">
+        <v>45</v>
+      </c>
+      <c r="I62">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" t="s">
         <v>33</v>
-      </c>
-      <c r="D62">
-        <v>3</v>
-      </c>
-      <c r="E62">
-        <v>45</v>
-      </c>
-      <c r="F62">
-        <v>15</v>
-      </c>
-      <c r="G62">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>46</v>
-      </c>
-      <c r="B63" t="s">
-        <v>27</v>
-      </c>
-      <c r="C63" t="s">
-        <v>34</v>
       </c>
       <c r="D63">
         <v>4</v>
@@ -2073,16 +2522,22 @@
       <c r="G63">
         <v>53</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H63">
+        <v>57</v>
+      </c>
+      <c r="I63">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C64" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D64">
         <v>4</v>
@@ -2096,39 +2551,51 @@
       <c r="G64">
         <v>53</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H64">
+        <v>57</v>
+      </c>
+      <c r="I64">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B65" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C65" t="s">
+        <v>60</v>
+      </c>
+      <c r="D65">
+        <v>3</v>
+      </c>
+      <c r="E65">
+        <v>45</v>
+      </c>
+      <c r="F65">
+        <v>15</v>
+      </c>
+      <c r="G65">
+        <v>42</v>
+      </c>
+      <c r="H65">
+        <v>45</v>
+      </c>
+      <c r="I65">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>45</v>
+      </c>
+      <c r="B66" t="s">
+        <v>35</v>
+      </c>
+      <c r="C66" t="s">
         <v>61</v>
-      </c>
-      <c r="D65">
-        <v>3</v>
-      </c>
-      <c r="E65">
-        <v>45</v>
-      </c>
-      <c r="F65">
-        <v>15</v>
-      </c>
-      <c r="G65">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>46</v>
-      </c>
-      <c r="B66" t="s">
-        <v>36</v>
-      </c>
-      <c r="C66" t="s">
-        <v>62</v>
       </c>
       <c r="D66">
         <v>2</v>
@@ -2142,40 +2609,52 @@
       <c r="G66">
         <v>21</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H66">
+        <v>23</v>
+      </c>
+      <c r="I66">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B67" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C67" t="s">
+        <v>62</v>
+      </c>
+      <c r="D67">
+        <v>3</v>
+      </c>
+      <c r="E67">
+        <v>45</v>
+      </c>
+      <c r="F67">
+        <v>15</v>
+      </c>
+      <c r="G67">
+        <v>42</v>
+      </c>
+      <c r="H67">
+        <v>45</v>
+      </c>
+      <c r="I67">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>45</v>
+      </c>
+      <c r="B68" t="s">
+        <v>35</v>
+      </c>
+      <c r="C68" t="s">
         <v>63</v>
       </c>
-      <c r="D67">
-        <v>3</v>
-      </c>
-      <c r="E67">
-        <v>45</v>
-      </c>
-      <c r="F67">
-        <v>15</v>
-      </c>
-      <c r="G67">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>46</v>
-      </c>
-      <c r="B68" t="s">
-        <v>36</v>
-      </c>
-      <c r="C68" t="s">
-        <v>64</v>
-      </c>
       <c r="D68">
         <v>3</v>
       </c>
@@ -2188,40 +2667,52 @@
       <c r="G68">
         <v>42</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H68">
+        <v>45</v>
+      </c>
+      <c r="I68">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B69" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C69" t="s">
+        <v>40</v>
+      </c>
+      <c r="D69">
+        <v>3</v>
+      </c>
+      <c r="E69">
+        <v>45</v>
+      </c>
+      <c r="F69">
+        <v>15</v>
+      </c>
+      <c r="G69">
+        <v>42</v>
+      </c>
+      <c r="H69">
+        <v>45</v>
+      </c>
+      <c r="I69">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>45</v>
+      </c>
+      <c r="B70" t="s">
+        <v>35</v>
+      </c>
+      <c r="C70" t="s">
         <v>41</v>
       </c>
-      <c r="D69">
-        <v>3</v>
-      </c>
-      <c r="E69">
-        <v>45</v>
-      </c>
-      <c r="F69">
-        <v>15</v>
-      </c>
-      <c r="G69">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>46</v>
-      </c>
-      <c r="B70" t="s">
-        <v>36</v>
-      </c>
-      <c r="C70" t="s">
-        <v>42</v>
-      </c>
       <c r="D70">
         <v>3</v>
       </c>
@@ -2234,16 +2725,22 @@
       <c r="G70">
         <v>42</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H70">
+        <v>45</v>
+      </c>
+      <c r="I70">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C71" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D71">
         <v>4</v>
@@ -2257,39 +2754,51 @@
       <c r="G71">
         <v>53</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H71">
+        <v>57</v>
+      </c>
+      <c r="I71">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C72" t="s">
+        <v>43</v>
+      </c>
+      <c r="D72">
+        <v>3</v>
+      </c>
+      <c r="E72">
+        <v>45</v>
+      </c>
+      <c r="F72">
+        <v>15</v>
+      </c>
+      <c r="G72">
+        <v>42</v>
+      </c>
+      <c r="H72">
+        <v>45</v>
+      </c>
+      <c r="I72">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>45</v>
+      </c>
+      <c r="B73" t="s">
+        <v>35</v>
+      </c>
+      <c r="C73" t="s">
         <v>44</v>
-      </c>
-      <c r="D72">
-        <v>3</v>
-      </c>
-      <c r="E72">
-        <v>45</v>
-      </c>
-      <c r="F72">
-        <v>15</v>
-      </c>
-      <c r="G72">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>46</v>
-      </c>
-      <c r="B73" t="s">
-        <v>36</v>
-      </c>
-      <c r="C73" t="s">
-        <v>45</v>
       </c>
       <c r="D73">
         <v>4</v>
@@ -2302,6 +2811,1172 @@
       </c>
       <c r="G73">
         <v>53</v>
+      </c>
+      <c r="H73">
+        <v>57</v>
+      </c>
+      <c r="I73">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>6</v>
+      </c>
+      <c r="B74" t="s">
+        <v>64</v>
+      </c>
+      <c r="C74" t="s">
+        <v>65</v>
+      </c>
+      <c r="D74">
+        <v>4</v>
+      </c>
+      <c r="E74">
+        <v>60</v>
+      </c>
+      <c r="F74">
+        <v>15</v>
+      </c>
+      <c r="G74">
+        <v>53</v>
+      </c>
+      <c r="H74">
+        <v>57</v>
+      </c>
+      <c r="I74">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>6</v>
+      </c>
+      <c r="B75" t="s">
+        <v>64</v>
+      </c>
+      <c r="C75" t="s">
+        <v>66</v>
+      </c>
+      <c r="D75">
+        <v>4</v>
+      </c>
+      <c r="E75">
+        <v>60</v>
+      </c>
+      <c r="F75">
+        <v>15</v>
+      </c>
+      <c r="G75">
+        <v>53</v>
+      </c>
+      <c r="H75">
+        <v>57</v>
+      </c>
+      <c r="I75">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>6</v>
+      </c>
+      <c r="B76" t="s">
+        <v>64</v>
+      </c>
+      <c r="C76" t="s">
+        <v>67</v>
+      </c>
+      <c r="D76">
+        <v>3</v>
+      </c>
+      <c r="E76">
+        <v>45</v>
+      </c>
+      <c r="F76">
+        <v>15</v>
+      </c>
+      <c r="G76">
+        <v>42</v>
+      </c>
+      <c r="H76">
+        <v>45</v>
+      </c>
+      <c r="I76">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>6</v>
+      </c>
+      <c r="B77" t="s">
+        <v>64</v>
+      </c>
+      <c r="C77" t="s">
+        <v>68</v>
+      </c>
+      <c r="D77">
+        <v>4</v>
+      </c>
+      <c r="E77">
+        <v>60</v>
+      </c>
+      <c r="F77">
+        <v>15</v>
+      </c>
+      <c r="G77">
+        <v>53</v>
+      </c>
+      <c r="H77">
+        <v>57</v>
+      </c>
+      <c r="I77">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>6</v>
+      </c>
+      <c r="B78" t="s">
+        <v>64</v>
+      </c>
+      <c r="C78" t="s">
+        <v>69</v>
+      </c>
+      <c r="D78">
+        <v>4</v>
+      </c>
+      <c r="E78">
+        <v>60</v>
+      </c>
+      <c r="F78">
+        <v>15</v>
+      </c>
+      <c r="G78">
+        <v>53</v>
+      </c>
+      <c r="H78">
+        <v>57</v>
+      </c>
+      <c r="I78">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>6</v>
+      </c>
+      <c r="B79" t="s">
+        <v>64</v>
+      </c>
+      <c r="C79" t="s">
+        <v>70</v>
+      </c>
+      <c r="D79">
+        <v>3</v>
+      </c>
+      <c r="E79">
+        <v>45</v>
+      </c>
+      <c r="F79">
+        <v>15</v>
+      </c>
+      <c r="G79">
+        <v>42</v>
+      </c>
+      <c r="H79">
+        <v>45</v>
+      </c>
+      <c r="I79">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" t="s">
+        <v>64</v>
+      </c>
+      <c r="C80" t="s">
+        <v>71</v>
+      </c>
+      <c r="D80">
+        <v>4</v>
+      </c>
+      <c r="E80">
+        <v>60</v>
+      </c>
+      <c r="F80">
+        <v>15</v>
+      </c>
+      <c r="G80">
+        <v>53</v>
+      </c>
+      <c r="H80">
+        <v>57</v>
+      </c>
+      <c r="I80">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>6</v>
+      </c>
+      <c r="B81" t="s">
+        <v>64</v>
+      </c>
+      <c r="C81" t="s">
+        <v>72</v>
+      </c>
+      <c r="D81">
+        <v>2</v>
+      </c>
+      <c r="E81">
+        <v>30</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>21</v>
+      </c>
+      <c r="H81">
+        <v>23</v>
+      </c>
+      <c r="I81">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>6</v>
+      </c>
+      <c r="B82" t="s">
+        <v>64</v>
+      </c>
+      <c r="C82" t="s">
+        <v>73</v>
+      </c>
+      <c r="D82">
+        <v>2</v>
+      </c>
+      <c r="E82">
+        <v>30</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>21</v>
+      </c>
+      <c r="H82">
+        <v>23</v>
+      </c>
+      <c r="I82">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>6</v>
+      </c>
+      <c r="B83" t="s">
+        <v>64</v>
+      </c>
+      <c r="C83" t="s">
+        <v>74</v>
+      </c>
+      <c r="D83">
+        <v>2</v>
+      </c>
+      <c r="E83">
+        <v>30</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>21</v>
+      </c>
+      <c r="H83">
+        <v>23</v>
+      </c>
+      <c r="I83">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84" t="s">
+        <v>64</v>
+      </c>
+      <c r="C84" t="s">
+        <v>75</v>
+      </c>
+      <c r="D84">
+        <v>2</v>
+      </c>
+      <c r="E84">
+        <v>30</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>21</v>
+      </c>
+      <c r="H84">
+        <v>23</v>
+      </c>
+      <c r="I84">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>45</v>
+      </c>
+      <c r="B85" t="s">
+        <v>64</v>
+      </c>
+      <c r="C85" t="s">
+        <v>65</v>
+      </c>
+      <c r="D85">
+        <v>4</v>
+      </c>
+      <c r="E85">
+        <v>60</v>
+      </c>
+      <c r="F85">
+        <v>15</v>
+      </c>
+      <c r="G85">
+        <v>53</v>
+      </c>
+      <c r="H85">
+        <v>57</v>
+      </c>
+      <c r="I85">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>45</v>
+      </c>
+      <c r="B86" t="s">
+        <v>64</v>
+      </c>
+      <c r="C86" t="s">
+        <v>66</v>
+      </c>
+      <c r="D86">
+        <v>4</v>
+      </c>
+      <c r="E86">
+        <v>60</v>
+      </c>
+      <c r="F86">
+        <v>15</v>
+      </c>
+      <c r="G86">
+        <v>53</v>
+      </c>
+      <c r="H86">
+        <v>57</v>
+      </c>
+      <c r="I86">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>45</v>
+      </c>
+      <c r="B87" t="s">
+        <v>64</v>
+      </c>
+      <c r="C87" t="s">
+        <v>67</v>
+      </c>
+      <c r="D87">
+        <v>3</v>
+      </c>
+      <c r="E87">
+        <v>45</v>
+      </c>
+      <c r="F87">
+        <v>15</v>
+      </c>
+      <c r="G87">
+        <v>42</v>
+      </c>
+      <c r="H87">
+        <v>45</v>
+      </c>
+      <c r="I87">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>45</v>
+      </c>
+      <c r="B88" t="s">
+        <v>64</v>
+      </c>
+      <c r="C88" t="s">
+        <v>68</v>
+      </c>
+      <c r="D88">
+        <v>4</v>
+      </c>
+      <c r="E88">
+        <v>60</v>
+      </c>
+      <c r="F88">
+        <v>15</v>
+      </c>
+      <c r="G88">
+        <v>53</v>
+      </c>
+      <c r="H88">
+        <v>57</v>
+      </c>
+      <c r="I88">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>45</v>
+      </c>
+      <c r="B89" t="s">
+        <v>64</v>
+      </c>
+      <c r="C89" t="s">
+        <v>69</v>
+      </c>
+      <c r="D89">
+        <v>4</v>
+      </c>
+      <c r="E89">
+        <v>60</v>
+      </c>
+      <c r="F89">
+        <v>15</v>
+      </c>
+      <c r="G89">
+        <v>53</v>
+      </c>
+      <c r="H89">
+        <v>57</v>
+      </c>
+      <c r="I89">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>45</v>
+      </c>
+      <c r="B90" t="s">
+        <v>64</v>
+      </c>
+      <c r="C90" t="s">
+        <v>70</v>
+      </c>
+      <c r="D90">
+        <v>3</v>
+      </c>
+      <c r="E90">
+        <v>45</v>
+      </c>
+      <c r="F90">
+        <v>15</v>
+      </c>
+      <c r="G90">
+        <v>42</v>
+      </c>
+      <c r="H90">
+        <v>45</v>
+      </c>
+      <c r="I90">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>45</v>
+      </c>
+      <c r="B91" t="s">
+        <v>64</v>
+      </c>
+      <c r="C91" t="s">
+        <v>71</v>
+      </c>
+      <c r="D91">
+        <v>4</v>
+      </c>
+      <c r="E91">
+        <v>60</v>
+      </c>
+      <c r="F91">
+        <v>15</v>
+      </c>
+      <c r="G91">
+        <v>53</v>
+      </c>
+      <c r="H91">
+        <v>57</v>
+      </c>
+      <c r="I91">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>45</v>
+      </c>
+      <c r="B92" t="s">
+        <v>64</v>
+      </c>
+      <c r="C92" t="s">
+        <v>72</v>
+      </c>
+      <c r="D92">
+        <v>2</v>
+      </c>
+      <c r="E92">
+        <v>30</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>21</v>
+      </c>
+      <c r="H92">
+        <v>23</v>
+      </c>
+      <c r="I92">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>45</v>
+      </c>
+      <c r="B93" t="s">
+        <v>64</v>
+      </c>
+      <c r="C93" t="s">
+        <v>73</v>
+      </c>
+      <c r="D93">
+        <v>2</v>
+      </c>
+      <c r="E93">
+        <v>30</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>21</v>
+      </c>
+      <c r="H93">
+        <v>23</v>
+      </c>
+      <c r="I93">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>45</v>
+      </c>
+      <c r="B94" t="s">
+        <v>64</v>
+      </c>
+      <c r="C94" t="s">
+        <v>74</v>
+      </c>
+      <c r="D94">
+        <v>2</v>
+      </c>
+      <c r="E94">
+        <v>30</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>21</v>
+      </c>
+      <c r="H94">
+        <v>23</v>
+      </c>
+      <c r="I94">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>45</v>
+      </c>
+      <c r="B95" t="s">
+        <v>64</v>
+      </c>
+      <c r="C95" t="s">
+        <v>75</v>
+      </c>
+      <c r="D95">
+        <v>2</v>
+      </c>
+      <c r="E95">
+        <v>30</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>21</v>
+      </c>
+      <c r="H95">
+        <v>23</v>
+      </c>
+      <c r="I95">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>6</v>
+      </c>
+      <c r="B96" t="s">
+        <v>76</v>
+      </c>
+      <c r="C96" t="s">
+        <v>77</v>
+      </c>
+      <c r="D96">
+        <v>4</v>
+      </c>
+      <c r="E96">
+        <v>60</v>
+      </c>
+      <c r="F96">
+        <v>15</v>
+      </c>
+      <c r="G96">
+        <v>53</v>
+      </c>
+      <c r="H96">
+        <v>57</v>
+      </c>
+      <c r="I96">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>6</v>
+      </c>
+      <c r="B97" t="s">
+        <v>76</v>
+      </c>
+      <c r="C97" t="s">
+        <v>78</v>
+      </c>
+      <c r="D97">
+        <v>3</v>
+      </c>
+      <c r="E97">
+        <v>45</v>
+      </c>
+      <c r="F97">
+        <v>15</v>
+      </c>
+      <c r="G97">
+        <v>42</v>
+      </c>
+      <c r="H97">
+        <v>45</v>
+      </c>
+      <c r="I97">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>6</v>
+      </c>
+      <c r="B98" t="s">
+        <v>76</v>
+      </c>
+      <c r="C98" t="s">
+        <v>79</v>
+      </c>
+      <c r="D98">
+        <v>4</v>
+      </c>
+      <c r="E98">
+        <v>60</v>
+      </c>
+      <c r="F98">
+        <v>15</v>
+      </c>
+      <c r="G98">
+        <v>53</v>
+      </c>
+      <c r="H98">
+        <v>57</v>
+      </c>
+      <c r="I98">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>6</v>
+      </c>
+      <c r="B99" t="s">
+        <v>76</v>
+      </c>
+      <c r="C99" t="s">
+        <v>80</v>
+      </c>
+      <c r="D99">
+        <v>4</v>
+      </c>
+      <c r="E99">
+        <v>60</v>
+      </c>
+      <c r="F99">
+        <v>15</v>
+      </c>
+      <c r="G99">
+        <v>53</v>
+      </c>
+      <c r="H99">
+        <v>57</v>
+      </c>
+      <c r="I99">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>6</v>
+      </c>
+      <c r="B100" t="s">
+        <v>76</v>
+      </c>
+      <c r="C100" t="s">
+        <v>81</v>
+      </c>
+      <c r="D100">
+        <v>3</v>
+      </c>
+      <c r="E100">
+        <v>45</v>
+      </c>
+      <c r="F100">
+        <v>15</v>
+      </c>
+      <c r="G100">
+        <v>42</v>
+      </c>
+      <c r="H100">
+        <v>45</v>
+      </c>
+      <c r="I100">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>6</v>
+      </c>
+      <c r="B101" t="s">
+        <v>76</v>
+      </c>
+      <c r="C101" t="s">
+        <v>82</v>
+      </c>
+      <c r="D101">
+        <v>3</v>
+      </c>
+      <c r="E101">
+        <v>45</v>
+      </c>
+      <c r="F101">
+        <v>15</v>
+      </c>
+      <c r="G101">
+        <v>42</v>
+      </c>
+      <c r="H101">
+        <v>45</v>
+      </c>
+      <c r="I101">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>6</v>
+      </c>
+      <c r="B102" t="s">
+        <v>76</v>
+      </c>
+      <c r="C102" t="s">
+        <v>83</v>
+      </c>
+      <c r="D102">
+        <v>2</v>
+      </c>
+      <c r="E102">
+        <v>30</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>21</v>
+      </c>
+      <c r="H102">
+        <v>23</v>
+      </c>
+      <c r="I102">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>6</v>
+      </c>
+      <c r="B103" t="s">
+        <v>76</v>
+      </c>
+      <c r="C103" t="s">
+        <v>84</v>
+      </c>
+      <c r="D103">
+        <v>2</v>
+      </c>
+      <c r="E103">
+        <v>30</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>21</v>
+      </c>
+      <c r="H103">
+        <v>23</v>
+      </c>
+      <c r="I103">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>6</v>
+      </c>
+      <c r="B104" t="s">
+        <v>76</v>
+      </c>
+      <c r="C104" t="s">
+        <v>85</v>
+      </c>
+      <c r="D104">
+        <v>2</v>
+      </c>
+      <c r="E104">
+        <v>30</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>21</v>
+      </c>
+      <c r="H104">
+        <v>23</v>
+      </c>
+      <c r="I104">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>45</v>
+      </c>
+      <c r="B105" t="s">
+        <v>76</v>
+      </c>
+      <c r="C105" t="s">
+        <v>77</v>
+      </c>
+      <c r="D105">
+        <v>4</v>
+      </c>
+      <c r="E105">
+        <v>60</v>
+      </c>
+      <c r="F105">
+        <v>15</v>
+      </c>
+      <c r="G105">
+        <v>53</v>
+      </c>
+      <c r="H105">
+        <v>57</v>
+      </c>
+      <c r="I105">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>45</v>
+      </c>
+      <c r="B106" t="s">
+        <v>76</v>
+      </c>
+      <c r="C106" t="s">
+        <v>78</v>
+      </c>
+      <c r="D106">
+        <v>3</v>
+      </c>
+      <c r="E106">
+        <v>45</v>
+      </c>
+      <c r="F106">
+        <v>15</v>
+      </c>
+      <c r="G106">
+        <v>42</v>
+      </c>
+      <c r="H106">
+        <v>45</v>
+      </c>
+      <c r="I106">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>45</v>
+      </c>
+      <c r="B107" t="s">
+        <v>76</v>
+      </c>
+      <c r="C107" t="s">
+        <v>79</v>
+      </c>
+      <c r="D107">
+        <v>4</v>
+      </c>
+      <c r="E107">
+        <v>60</v>
+      </c>
+      <c r="F107">
+        <v>15</v>
+      </c>
+      <c r="G107">
+        <v>53</v>
+      </c>
+      <c r="H107">
+        <v>57</v>
+      </c>
+      <c r="I107">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>45</v>
+      </c>
+      <c r="B108" t="s">
+        <v>76</v>
+      </c>
+      <c r="C108" t="s">
+        <v>80</v>
+      </c>
+      <c r="D108">
+        <v>4</v>
+      </c>
+      <c r="E108">
+        <v>60</v>
+      </c>
+      <c r="F108">
+        <v>15</v>
+      </c>
+      <c r="G108">
+        <v>53</v>
+      </c>
+      <c r="H108">
+        <v>57</v>
+      </c>
+      <c r="I108">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>45</v>
+      </c>
+      <c r="B109" t="s">
+        <v>76</v>
+      </c>
+      <c r="C109" t="s">
+        <v>81</v>
+      </c>
+      <c r="D109">
+        <v>3</v>
+      </c>
+      <c r="E109">
+        <v>45</v>
+      </c>
+      <c r="F109">
+        <v>15</v>
+      </c>
+      <c r="G109">
+        <v>42</v>
+      </c>
+      <c r="H109">
+        <v>45</v>
+      </c>
+      <c r="I109">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>45</v>
+      </c>
+      <c r="B110" t="s">
+        <v>76</v>
+      </c>
+      <c r="C110" t="s">
+        <v>82</v>
+      </c>
+      <c r="D110">
+        <v>3</v>
+      </c>
+      <c r="E110">
+        <v>45</v>
+      </c>
+      <c r="F110">
+        <v>15</v>
+      </c>
+      <c r="G110">
+        <v>42</v>
+      </c>
+      <c r="H110">
+        <v>45</v>
+      </c>
+      <c r="I110">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>45</v>
+      </c>
+      <c r="B111" t="s">
+        <v>76</v>
+      </c>
+      <c r="C111" t="s">
+        <v>83</v>
+      </c>
+      <c r="D111">
+        <v>2</v>
+      </c>
+      <c r="E111">
+        <v>30</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>21</v>
+      </c>
+      <c r="H111">
+        <v>23</v>
+      </c>
+      <c r="I111">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>45</v>
+      </c>
+      <c r="B112" t="s">
+        <v>76</v>
+      </c>
+      <c r="C112" t="s">
+        <v>84</v>
+      </c>
+      <c r="D112">
+        <v>2</v>
+      </c>
+      <c r="E112">
+        <v>30</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>21</v>
+      </c>
+      <c r="H112">
+        <v>23</v>
+      </c>
+      <c r="I112">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>45</v>
+      </c>
+      <c r="B113" t="s">
+        <v>76</v>
+      </c>
+      <c r="C113" t="s">
+        <v>85</v>
+      </c>
+      <c r="D113">
+        <v>2</v>
+      </c>
+      <c r="E113">
+        <v>30</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>21</v>
+      </c>
+      <c r="H113">
+        <v>23</v>
+      </c>
+      <c r="I113">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
